--- a/Documentation/Week 4/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 4/Booked Hours/Booked_Hours_Christo.xlsx
@@ -1,28 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelw/CSSE/CITS3200/Administrivia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 4/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{770FC887-8886-43E0-822B-3B859C184730}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="460" windowWidth="21780" windowHeight="15340" tabRatio="500"/>
+    <workbookView xWindow="2730" yWindow="2625" windowWidth="20475" windowHeight="20745" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="22">
   <si>
     <t>Wk</t>
   </si>
@@ -50,8 +63,14 @@
 Hours</t>
   </si>
   <si>
+    <t>Researching group project requirements, getting familiar with project documentation, writing agenda</t>
+  </si>
+  <si>
+    <t>Team meeting</t>
+  </si>
+  <si>
     <r>
-      <t>CITS3200 Project Billed Hours Record for &lt;YOUR NAME GOES HERE&gt;</t>
+      <t>CITS3200 Project Billed Hours Record for &lt;Christo Wesseloo&gt;</t>
     </r>
     <r>
       <rPr>
@@ -63,12 +82,45 @@
 Each time you do some work on the project, note the week number, start and end date and hour, plus a brief description of the activity. At the end of each week send a copy of the sheet as it currently stands to your group's manager for recording on the group TimeSheet. Date in the form DD/MM/YY and time as XX:YY (24hr clock)</t>
     </r>
   </si>
+  <si>
+    <t>Writing up team documentation as well as researching project information</t>
+  </si>
+  <si>
+    <t>Client meeting</t>
+  </si>
+  <si>
+    <t>Finishing meeting minutes</t>
+  </si>
+  <si>
+    <t>Filling in Team Timesheet</t>
+  </si>
+  <si>
+    <t>Project / scope research</t>
+  </si>
+  <si>
+    <t>Meeting documentation</t>
+  </si>
+  <si>
+    <t>Skills and Resources Audit</t>
+  </si>
+  <si>
+    <t>Setting up project environment</t>
+  </si>
+  <si>
+    <t>Writing up procedure for setting up Ubuntu project environment</t>
+  </si>
+  <si>
+    <t>Writing meeting agenda</t>
+  </si>
+  <si>
+    <t>Filling in team timesheet</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Verdana"/>
@@ -281,6 +333,10 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -295,10 +351,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -321,7 +373,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -735,25 +787,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="46.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" style="1"/>
-    <col min="9" max="9" width="10.6640625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.6640625" style="1"/>
+    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1"/>
+    <col min="9" max="9" width="10.625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="71" customHeight="1">
+    <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -763,30 +815,30 @@
       <c r="G1" s="13"/>
       <c r="H1" s="14"/>
     </row>
-    <row r="2" spans="1:9" ht="16" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="10"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13" customHeight="1">
-      <c r="A3" s="8"/>
+    <row r="3" spans="1:9" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
@@ -800,286 +852,496 @@
         <v>3</v>
       </c>
       <c r="F3" s="18"/>
-      <c r="G3" s="8"/>
+      <c r="G3" s="9"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:9">
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-      <c r="G4" s="6" t="str">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4">
+        <v>44770</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D4" s="4">
+        <v>44770</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.40625</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="6">
         <f>IF(I4&gt;0,I4,IF(I4=0, " ", "ERROR"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H4" s="1" t="str">
+        <v>1.2500000000582077</v>
+      </c>
+      <c r="H4" s="1">
         <f>IF(G4&lt;&gt;"ERROR",G4)</f>
-        <v xml:space="preserve"> </v>
+        <v>1.2500000000582077</v>
       </c>
       <c r="I4" s="1">
-        <f>((D4+E4)-(B4+C4))*24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="G5" s="6" t="str">
-        <f t="shared" ref="G5:G30" si="0">IF(I5&gt;0,I5,IF(I5=0, " ", "ERROR"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H5" s="1" t="str">
+        <f t="shared" ref="I4:I35" si="0">((D4+E4)-(B4+C4))*24</f>
+        <v>1.2500000000582077</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4">
+        <v>44770</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="4">
+        <v>44770</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" ref="G5:G30" si="1">IF(I5&gt;0,I5,IF(I5=0, " ", "ERROR"))</f>
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="H5" s="1">
         <f>IF(AND(G5&lt;&gt;" ",G5&lt;&gt;"ERROR",H4&lt;&gt;" ", H4&lt;&gt;"ERROR"),G5+H4," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>2.25</v>
       </c>
       <c r="I5" s="1">
-        <f t="shared" ref="I5:I68" si="1">((D5+E5)-(B5+C5))*24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="G6" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H6" s="1" t="str">
+        <v>0.99999999994179234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4">
+        <v>44770</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D6" s="4">
+        <v>44770</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="6">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="H6" s="1">
         <f t="shared" ref="H6:H30" si="2">IF(AND(G6&lt;&gt;" ",G6&lt;&gt;"ERROR",H5&lt;&gt;" ", H5&lt;&gt;"ERROR"),G6+H5," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>3</v>
       </c>
       <c r="I6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4">
+        <v>44771</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.5625</v>
+      </c>
+      <c r="D7" s="4">
+        <v>44771</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="G7" s="6" t="str">
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="2"/>
+        <v>3.9999999999417923</v>
+      </c>
+      <c r="I7" s="1">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H7" s="1" t="str">
+        <v>0.99999999994179234</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4">
+        <v>44771</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D8" s="4">
+        <v>44771</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" si="1"/>
+        <v>0.50000000005820766</v>
+      </c>
+      <c r="H8" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I7" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="0"/>
+        <v>0.50000000005820766</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="4">
+        <v>44772</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D9" s="4">
+        <v>44772</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.8125</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-      <c r="G8" s="6" t="str">
+        <v>0.50000000005820766</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="2"/>
+        <v>5.0000000000582077</v>
+      </c>
+      <c r="I9" s="1">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H8" s="1" t="str">
+        <v>0.50000000005820766</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="4">
+        <v>44777</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D10" s="4">
+        <v>44777</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.40625</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" si="1"/>
+        <v>1.2500000000582077</v>
+      </c>
+      <c r="H10" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I8" s="1">
+        <v>6.2500000001164153</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" si="0"/>
+        <v>1.2500000000582077</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="4">
+        <v>44777</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="4">
+        <v>44777</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="G9" s="6" t="str">
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="2"/>
+        <v>7.2500000000582077</v>
+      </c>
+      <c r="I11" s="1">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H9" s="1" t="str">
+        <v>0.99999999994179234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>3</v>
+      </c>
+      <c r="B12" s="4">
+        <v>44777</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D12" s="4">
+        <v>44777</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="6">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="H12" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I9" s="1">
+        <v>8.0000000000582077</v>
+      </c>
+      <c r="I12" s="1">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>3</v>
+      </c>
+      <c r="B13" s="4">
+        <v>44777</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D13" s="4">
+        <v>44777</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
-      <c r="G10" s="6" t="str">
+        <v>1.2499999998835847</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="2"/>
+        <v>9.2499999999417923</v>
+      </c>
+      <c r="I13" s="1">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H10" s="1" t="str">
+        <v>1.2499999998835847</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>3</v>
+      </c>
+      <c r="B14" s="4">
+        <v>44778</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D14" s="4">
+        <v>44778</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="6">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="H14" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I10" s="1">
+        <v>9.9999999999417923</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>3</v>
+      </c>
+      <c r="B15" s="4">
+        <v>44779</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D15" s="4">
+        <v>44779</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-      <c r="G11" s="6" t="str">
+        <v>0.50000000005820766</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="2"/>
+        <v>10.5</v>
+      </c>
+      <c r="I15" s="1">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H11" s="1" t="str">
+        <v>0.50000000005820766</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>4</v>
+      </c>
+      <c r="B16" s="4">
+        <v>44782</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D16" s="4">
+        <v>44782</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="6">
+        <f t="shared" si="1"/>
+        <v>0.25000000011641532</v>
+      </c>
+      <c r="H16" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I11" s="1">
+        <v>10.750000000116415</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" si="0"/>
+        <v>0.25000000011641532</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>4</v>
+      </c>
+      <c r="B17" s="4">
+        <v>44782</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D17" s="4">
+        <v>44782</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="G12" s="6" t="str">
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="2"/>
+        <v>11.750000000058208</v>
+      </c>
+      <c r="I17" s="1">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H12" s="1" t="str">
+        <v>0.99999999994179234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>4</v>
+      </c>
+      <c r="B18" s="4">
+        <v>44782</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="D18" s="4">
+        <v>44782</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="6">
+        <f t="shared" si="1"/>
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="H18" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I12" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="B13" s="4"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-      <c r="G13" s="6" t="str">
+        <v>12.75</v>
+      </c>
+      <c r="I18" s="1">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H13" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I13" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5"/>
-      <c r="G14" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H14" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I14" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
-      <c r="G15" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H15" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I15" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
-      <c r="G16" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H16" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I16" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="B17" s="4"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="G17" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H17" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I17" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
-      <c r="G18" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H18" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I18" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>0.99999999994179234</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
       <c r="D19" s="4"/>
       <c r="E19" s="5"/>
       <c r="G19" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H19" s="1" t="str">
@@ -1087,17 +1349,17 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I19" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
       <c r="D20" s="4"/>
       <c r="E20" s="5"/>
       <c r="G20" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H20" s="1" t="str">
@@ -1105,17 +1367,17 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I20" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
       <c r="D21" s="4"/>
       <c r="E21" s="5"/>
       <c r="G21" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H21" s="1" t="str">
@@ -1123,17 +1385,17 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I21" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B22" s="4"/>
       <c r="C22" s="5"/>
       <c r="D22" s="4"/>
       <c r="E22" s="5"/>
       <c r="G22" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H22" s="1" t="str">
@@ -1141,17 +1403,17 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I22" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B23" s="4"/>
       <c r="C23" s="5"/>
       <c r="D23" s="4"/>
       <c r="E23" s="5"/>
       <c r="G23" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H23" s="1" t="str">
@@ -1159,17 +1421,17 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I23" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
       <c r="D24" s="4"/>
       <c r="E24" s="5"/>
       <c r="G24" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H24" s="1" t="str">
@@ -1177,17 +1439,17 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I24" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
       <c r="D25" s="4"/>
       <c r="E25" s="5"/>
       <c r="G25" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H25" s="1" t="str">
@@ -1195,17 +1457,17 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I25" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
       <c r="D26" s="4"/>
       <c r="E26" s="5"/>
       <c r="G26" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H26" s="1" t="str">
@@ -1213,17 +1475,17 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I26" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
       <c r="D27" s="4"/>
       <c r="E27" s="5"/>
       <c r="G27" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H27" s="1" t="str">
@@ -1231,17 +1493,17 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I27" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
       <c r="D28" s="4"/>
       <c r="E28" s="5"/>
       <c r="G28" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H28" s="1" t="str">
@@ -1249,17 +1511,17 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I28" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
       <c r="D29" s="4"/>
       <c r="E29" s="5"/>
       <c r="G29" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H29" s="1" t="str">
@@ -1267,17 +1529,17 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I29" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
       <c r="D30" s="4"/>
       <c r="E30" s="5"/>
       <c r="G30" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H30" s="1" t="str">
@@ -1285,38 +1547,38 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I30" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="16">
-      <c r="A31" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="9" t="s">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="9" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="10"/>
-      <c r="F31" s="11" t="s">
+      <c r="E31" s="11"/>
+      <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I31" s="1" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="16">
-      <c r="A32" s="8"/>
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="9"/>
       <c r="B32" s="2" t="s">
         <v>2</v>
       </c>
@@ -1329,15 +1591,15 @@
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
       <c r="I32" s="1" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="2:9">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
       <c r="D33" s="4"/>
@@ -1351,11 +1613,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I33" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
       <c r="D34" s="4"/>
@@ -1369,11 +1631,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I34" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
       <c r="D35" s="4"/>
@@ -1387,11 +1649,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I35" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="4"/>
@@ -1405,11 +1667,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I36" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9">
+        <f t="shared" ref="I36:I68" si="5">((D36+E36)-(B36+C36))*24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
       <c r="D37" s="4"/>
@@ -1423,11 +1685,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
       <c r="D38" s="4"/>
@@ -1441,11 +1703,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I38" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
       <c r="D39" s="4"/>
@@ -1459,11 +1721,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I39" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="4"/>
@@ -1477,11 +1739,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I40" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="4"/>
@@ -1495,11 +1757,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I41" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B42" s="4"/>
       <c r="C42" s="5"/>
       <c r="D42" s="4"/>
@@ -1513,11 +1775,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I42" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
       <c r="D43" s="4"/>
@@ -1531,11 +1793,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I43" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
       <c r="D44" s="4"/>
@@ -1549,11 +1811,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I44" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
       <c r="D45" s="4"/>
@@ -1567,11 +1829,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I45" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
       <c r="D46" s="4"/>
@@ -1585,11 +1847,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I46" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
       <c r="D47" s="4"/>
@@ -1603,11 +1865,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I47" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="4"/>
       <c r="C48" s="5"/>
       <c r="D48" s="4"/>
@@ -1621,11 +1883,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I48" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B49" s="4"/>
       <c r="C49" s="5"/>
       <c r="D49" s="4"/>
@@ -1639,11 +1901,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I49" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B50" s="4"/>
       <c r="C50" s="5"/>
       <c r="D50" s="4"/>
@@ -1657,11 +1919,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I50" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51" s="4"/>
       <c r="C51" s="5"/>
       <c r="D51" s="4"/>
@@ -1675,11 +1937,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="4"/>
       <c r="C52" s="5"/>
       <c r="D52" s="4"/>
@@ -1693,11 +1955,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I52" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="4"/>
       <c r="C53" s="5"/>
       <c r="D53" s="4"/>
@@ -1711,11 +1973,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I53" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
       <c r="D54" s="4"/>
@@ -1729,11 +1991,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I54" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="4"/>
       <c r="C55" s="5"/>
       <c r="D55" s="4"/>
@@ -1747,11 +2009,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I55" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B56" s="4"/>
       <c r="C56" s="5"/>
       <c r="D56" s="4"/>
@@ -1765,11 +2027,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I56" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B57" s="4"/>
       <c r="C57" s="5"/>
       <c r="D57" s="4"/>
@@ -1783,11 +2045,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I57" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="4"/>
       <c r="C58" s="5"/>
       <c r="D58" s="4"/>
@@ -1801,11 +2063,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I58" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="4"/>
       <c r="C59" s="5"/>
       <c r="D59" s="4"/>
@@ -1819,11 +2081,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I59" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="4"/>
       <c r="G60" s="6" t="str">
         <f t="shared" si="3"/>
@@ -1834,11 +2096,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I60" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B61" s="4"/>
       <c r="G61" s="6" t="str">
         <f t="shared" si="3"/>
@@ -1849,11 +2111,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I61" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B62" s="4"/>
       <c r="G62" s="6" t="str">
         <f t="shared" si="3"/>
@@ -1864,11 +2126,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I62" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="4"/>
       <c r="G63" s="6" t="str">
         <f t="shared" si="3"/>
@@ -1879,11 +2141,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I63" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B64" s="4"/>
       <c r="G64" s="6" t="str">
         <f t="shared" si="3"/>
@@ -1894,38 +2156,38 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I64" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="16">
-      <c r="A65" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" s="9" t="s">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A65" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="9" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="10"/>
-      <c r="F65" s="11" t="s">
+      <c r="E65" s="11"/>
+      <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G65" s="11" t="s">
+      <c r="G65" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I65" s="1" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="16">
-      <c r="A66" s="8"/>
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A66" s="9"/>
       <c r="B66" s="2" t="s">
         <v>2</v>
       </c>
@@ -1938,17 +2200,17 @@
       <c r="E66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="11"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
       <c r="I66" s="1" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G67" s="6" t="str">
-        <f t="shared" ref="G67:G98" si="5">IF(I67&gt;0,I67,IF(I67=0, " ", "ERROR"))</f>
+        <f t="shared" ref="G67:G98" si="6">IF(I67&gt;0,I67,IF(I67=0, " ", "ERROR"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H67" s="1" t="str">
@@ -1956,472 +2218,472 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I67" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G68" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H68" s="1" t="str">
+        <f t="shared" ref="H68:H98" si="7">IF(AND(G68&lt;&gt;" ",G68&lt;&gt;"ERROR",H67&lt;&gt;" ", H67&lt;&gt;"ERROR"),G68+H67," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I68" s="1">
         <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H68" s="1" t="str">
-        <f t="shared" ref="H68:H98" si="6">IF(AND(G68&lt;&gt;" ",G68&lt;&gt;"ERROR",H67&lt;&gt;" ", H67&lt;&gt;"ERROR"),G68+H67," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I68" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G69" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H69" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I69" s="1">
+        <f t="shared" ref="I69:I132" si="8">((D69+E69)-(B69+C69))*24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G70" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I69" s="1">
-        <f t="shared" ref="I69:I132" si="7">((D69+E69)-(B69+C69))*24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
-      <c r="G70" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H70" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I70" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G71" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I70" s="1">
+      <c r="H71" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
-      <c r="G71" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H71" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I71" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G72" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I71" s="1">
+      <c r="H72" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
-      <c r="G72" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H72" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I72" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G73" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I72" s="1">
+      <c r="H73" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
-      <c r="G73" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H73" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I73" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G74" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I73" s="1">
+      <c r="H74" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
-      <c r="G74" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H74" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I74" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G75" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I74" s="1">
+      <c r="H75" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
-      <c r="G75" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H75" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I75" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G76" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I75" s="1">
+      <c r="H76" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
-      <c r="G76" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H76" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I76" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G77" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I76" s="1">
+      <c r="H77" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
-      <c r="G77" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H77" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I77" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G78" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I77" s="1">
+      <c r="H78" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
-      <c r="G78" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H78" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I78" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G79" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I78" s="1">
+      <c r="H79" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
-      <c r="G79" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H79" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I79" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G80" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I79" s="1">
+      <c r="H80" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
-      <c r="G80" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H80" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I80" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G81" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I80" s="1">
+      <c r="H81" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="7:9">
-      <c r="G81" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H81" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I81" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G82" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I81" s="1">
+      <c r="H82" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="7:9">
-      <c r="G82" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H82" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I82" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G83" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I82" s="1">
+      <c r="H83" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="7:9">
-      <c r="G83" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H83" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I83" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G84" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I83" s="1">
+      <c r="H84" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="7:9">
-      <c r="G84" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H84" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I84" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G85" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I84" s="1">
+      <c r="H85" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="7:9">
-      <c r="G85" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H85" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I85" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G86" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I85" s="1">
+      <c r="H86" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="7:9">
-      <c r="G86" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H86" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I86" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G87" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I86" s="1">
+      <c r="H87" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="7:9">
-      <c r="G87" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H87" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I87" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G88" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I87" s="1">
+      <c r="H88" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="7:9">
-      <c r="G88" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H88" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I88" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G89" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I88" s="1">
+      <c r="H89" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="7:9">
-      <c r="G89" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H89" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I89" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G90" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I89" s="1">
+      <c r="H90" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="7:9">
-      <c r="G90" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H90" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I90" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G91" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I90" s="1">
+      <c r="H91" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="7:9">
-      <c r="G91" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H91" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I91" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G92" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I91" s="1">
+      <c r="H92" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="7:9">
-      <c r="G92" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H92" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I92" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G93" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I92" s="1">
+      <c r="H93" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="7:9">
-      <c r="G93" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H93" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I93" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G94" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I93" s="1">
+      <c r="H94" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="7:9">
-      <c r="G94" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H94" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I94" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G95" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I94" s="1">
+      <c r="H95" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="7:9">
-      <c r="G95" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H95" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I95" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G96" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I95" s="1">
+      <c r="H96" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="7:9">
-      <c r="G96" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H96" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I96" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G97" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I96" s="1">
+      <c r="H97" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9">
-      <c r="G97" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H97" s="1" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I97" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G98" s="6" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I97" s="1">
+      <c r="H98" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9">
-      <c r="G98" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H98" s="1" t="str">
-        <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="I98" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="16">
-      <c r="A99" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="9" t="s">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A99" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="10"/>
-      <c r="D99" s="9" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="10"/>
-      <c r="F99" s="11" t="s">
+      <c r="E99" s="11"/>
+      <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G99" s="11" t="s">
+      <c r="G99" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H99" s="11" t="s">
+      <c r="H99" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I99" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="16">
-      <c r="A100" s="8"/>
+    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A100" s="9"/>
       <c r="B100" s="2" t="s">
         <v>2</v>
       </c>
@@ -2434,17 +2696,17 @@
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="11"/>
-      <c r="G100" s="11"/>
-      <c r="H100" s="11"/>
+      <c r="F100" s="7"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="7"/>
       <c r="I100" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G101" s="6" t="str">
-        <f t="shared" ref="G101:G132" si="8">IF(I101&gt;0,I101,IF(I101=0, " ", "ERROR"))</f>
+        <f t="shared" ref="G101:G132" si="9">IF(I101&gt;0,I101,IF(I101=0, " ", "ERROR"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H101" s="1" t="str">
@@ -2452,441 +2714,441 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I101" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G102" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H102" s="1" t="str">
-        <f t="shared" ref="H102:H132" si="9">IF(AND(G102&lt;&gt;" ",G102&lt;&gt;"ERROR",H101&lt;&gt;" ", H101&lt;&gt;"ERROR"),G102+H101," ")</f>
+        <f t="shared" ref="H102:H132" si="10">IF(AND(G102&lt;&gt;" ",G102&lt;&gt;"ERROR",H101&lt;&gt;" ", H101&lt;&gt;"ERROR"),G102+H101," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="I102" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G103" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H103" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I103" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G104" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I103" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9">
-      <c r="G104" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H104" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I104" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G105" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I104" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
-      <c r="G105" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H105" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I105" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G106" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I105" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9">
-      <c r="G106" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H106" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I106" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G107" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I106" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9">
-      <c r="G107" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H107" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I107" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G108" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I107" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9">
-      <c r="G108" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H108" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I108" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G109" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I108" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9">
-      <c r="G109" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H109" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I109" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G110" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I109" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9">
-      <c r="G110" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H110" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I110" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G111" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I110" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9">
-      <c r="G111" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H111" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I111" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G112" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I111" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9">
-      <c r="G112" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H112" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I112" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G113" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I112" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="7:9">
-      <c r="G113" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H113" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I113" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G114" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I113" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="7:9">
-      <c r="G114" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H114" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I114" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G115" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I114" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="7:9">
-      <c r="G115" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H115" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I115" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G116" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I115" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="7:9">
-      <c r="G116" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H116" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I116" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G117" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I116" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="7:9">
-      <c r="G117" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H117" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I117" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G118" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I117" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="7:9">
-      <c r="G118" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H118" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I118" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G119" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I118" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="7:9">
-      <c r="G119" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H119" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I119" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G120" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I119" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="7:9">
-      <c r="G120" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H120" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I120" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G121" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I120" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="7:9">
-      <c r="G121" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H121" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I121" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G122" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I121" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="7:9">
-      <c r="G122" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H122" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I122" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G123" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I122" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="7:9">
-      <c r="G123" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H123" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I123" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G124" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I123" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="7:9">
-      <c r="G124" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H124" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I124" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G125" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I124" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="7:9">
-      <c r="G125" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H125" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I125" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G126" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I125" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="7:9">
-      <c r="G126" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H126" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I126" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G127" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I126" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="7:9">
-      <c r="G127" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H127" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I127" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G128" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I127" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="7:9">
-      <c r="G128" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H128" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I128" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G129" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I128" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="7:9">
-      <c r="G129" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H129" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I129" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G130" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I129" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="7:9">
-      <c r="G130" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H130" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I130" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G131" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I130" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="7:9">
-      <c r="G131" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H131" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I131" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G132" s="6" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I131" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="7:9">
-      <c r="G132" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="H132" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="I132" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -2904,19 +3166,19 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G31:G32"/>
     <mergeCell ref="G65:G66"/>
     <mergeCell ref="H65:H66"/>
     <mergeCell ref="A65:A66"/>
     <mergeCell ref="B65:C65"/>
     <mergeCell ref="D65:E65"/>
     <mergeCell ref="F65:F66"/>
-    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="H99:H100"/>
     <mergeCell ref="A99:A100"/>
     <mergeCell ref="B99:C99"/>
     <mergeCell ref="D99:E99"/>
     <mergeCell ref="F99:F100"/>
     <mergeCell ref="G99:G100"/>
-    <mergeCell ref="H99:H100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -2926,9 +3188,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2938,9 +3200,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Documentation/Week 4/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 4/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 4/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{770FC887-8886-43E0-822B-3B859C184730}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4217C8C-C356-4D6E-99AA-D1CC67C9FE1A}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2625" windowWidth="20475" windowHeight="20745" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="11172" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="23">
   <si>
     <t>Wk</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>Filling in team timesheet</t>
+  </si>
+  <si>
+    <t>Group meeting</t>
   </si>
 </sst>
 </file>
@@ -345,14 +348,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -371,6 +366,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -804,36 +807,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -853,7 +856,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="16"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1336,57 +1339,99 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="4"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="5"/>
-      <c r="G19" s="6" t="str">
+      <c r="A19" s="1">
+        <v>4</v>
+      </c>
+      <c r="B19" s="4">
+        <v>44784</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D19" s="4">
+        <v>44784</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="6">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H19" s="1" t="str">
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="H19" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>13.749999999941792</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.99999999994179234</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B20" s="4"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="5"/>
-      <c r="G20" s="6" t="str">
+      <c r="A20" s="1">
+        <v>4</v>
+      </c>
+      <c r="B20" s="4">
+        <v>44784</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D20" s="4">
+        <v>44784</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="6">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H20" s="1" t="str">
+        <v>0.25000000011641532</v>
+      </c>
+      <c r="H20" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>14.000000000058208</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.25000000011641532</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="5"/>
-      <c r="G21" s="6" t="str">
+      <c r="A21" s="1">
+        <v>4</v>
+      </c>
+      <c r="B21" s="4">
+        <v>44784</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D21" s="4">
+        <v>44784</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="6">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H21" s="1" t="str">
+        <v>0.25000000011641532</v>
+      </c>
+      <c r="H21" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>14.250000000174623</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.25000000011641532</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
@@ -1555,14 +1600,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2164,14 +2209,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="16"/>
+      <c r="D65" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="11"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -2660,14 +2705,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="11"/>
-      <c r="D99" s="10" t="s">
+      <c r="C99" s="16"/>
+      <c r="D99" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3154,6 +3199,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3167,18 +3224,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 4/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 4/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 4/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4217C8C-C356-4D6E-99AA-D1CC67C9FE1A}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA6A02B1-CDAE-4BB4-9427-F477B7D4E4AB}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="11172" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="10008" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>Wk</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>Group meeting</t>
+  </si>
+  <si>
+    <t>Gesture Coding</t>
   </si>
 </sst>
 </file>
@@ -348,6 +351,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -366,14 +377,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -467,6 +470,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -792,55 +799,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1"/>
-    <col min="9" max="9" width="10.625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.625" style="1"/>
+    <col min="1" max="1" width="5.90625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6328125" style="1"/>
+    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -856,7 +863,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1435,21 +1442,35 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B22" s="4"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
-      <c r="G22" s="6" t="str">
+      <c r="A22" s="1">
+        <v>4</v>
+      </c>
+      <c r="B22" s="4">
+        <v>44786</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D22" s="4">
+        <v>44786</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="6">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H22" s="1" t="str">
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="H22" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>15.250000000116415</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.99999999994179234</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
@@ -1596,18 +1617,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -1622,7 +1643,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="2" t="s">
         <v>2</v>
@@ -2205,18 +2226,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -2231,7 +2252,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="9"/>
       <c r="B66" s="2" t="s">
         <v>2</v>
@@ -2701,18 +2722,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -2727,7 +2748,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="9"/>
       <c r="B100" s="2" t="s">
         <v>2</v>
@@ -3199,18 +3220,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3224,6 +3233,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -3235,7 +3256,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3247,7 +3268,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Documentation/Week 4/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 4/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 4/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA6A02B1-CDAE-4BB4-9427-F477B7D4E4AB}"/>
+  <xr:revisionPtr revIDLastSave="160" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F5E6078-BA4F-45F7-AD13-0D9573007453}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="10008" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="10008" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="23">
   <si>
     <t>Wk</t>
   </si>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>Finishing meeting minutes</t>
-  </si>
-  <si>
-    <t>Filling in Team Timesheet</t>
   </si>
   <si>
     <t>Project / scope research</t>
@@ -806,7 +803,7 @@
     <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="52.453125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
     <col min="8" max="8" width="10.6328125" style="1"/>
     <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
@@ -1042,7 +1039,7 @@
         <v>0.8125</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G9" s="6">
         <f t="shared" si="1"/>
@@ -1074,7 +1071,7 @@
         <v>0.40625</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10" s="6">
         <f t="shared" si="1"/>
@@ -1170,7 +1167,7 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13" s="6">
         <f t="shared" si="1"/>
@@ -1202,7 +1199,7 @@
         <v>0.36458333333333331</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G14" s="6">
         <f t="shared" si="1"/>
@@ -1234,7 +1231,7 @@
         <v>0.875</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G15" s="6">
         <f t="shared" si="1"/>
@@ -1266,7 +1263,7 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" s="6">
         <f t="shared" si="1"/>
@@ -1298,7 +1295,7 @@
         <v>0.75</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G17" s="6">
         <f t="shared" si="1"/>
@@ -1330,7 +1327,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" s="6">
         <f t="shared" si="1"/>
@@ -1362,7 +1359,7 @@
         <v>0.5</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G19" s="6">
         <f t="shared" si="1"/>
@@ -1426,7 +1423,7 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" s="6">
         <f t="shared" si="1"/>
@@ -1458,7 +1455,7 @@
         <v>0.75</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G22" s="6">
         <f t="shared" si="1"/>
@@ -1474,21 +1471,35 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
-      <c r="G23" s="6" t="str">
+      <c r="A23" s="1">
+        <v>4</v>
+      </c>
+      <c r="B23" s="4">
+        <v>44786</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="D23" s="4">
+        <v>44786</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="6">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H23" s="1" t="str">
+        <v>0.24999999994179234</v>
+      </c>
+      <c r="H23" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>15.500000000058208</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.24999999994179234</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
